--- a/education_forms/029_child_planning_form--education_forms.xlsx
+++ b/education_forms/029_child_planning_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -912,8 +912,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -941,12 +941,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'social_and_emotional_skills',_'value':_'social'}</t>
+          <t>social_and_emotional_skills</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Social and Emotional Skills', 'value': 'social'}</t>
+          <t>Social and Emotional Skills</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'literacy_and_language',_'value':_'literacy'}</t>
+          <t>literacy_and_language</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Literacy and Language', 'value': 'literacy'}</t>
+          <t>Literacy and Language</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'gross_and_fine_motor_skills',_'value':_'motor'}</t>
+          <t>gross_and_fine_motor_skills</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Gross and Fine Motor Skills', 'value': 'motor'}</t>
+          <t>Gross and Fine Motor Skills</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'cognitive_development',_'value':_'cognitive'}</t>
+          <t>cognitive_development</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Cognitive Development', 'value': 'cognitive'}</t>
+          <t>Cognitive Development</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'building_blocks_and_sets',_'value':_'blocks'}</t>
+          <t>building_blocks_and_sets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Building Blocks and Sets', 'value': 'blocks'}</t>
+          <t>Building Blocks and Sets</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'picture_and_story_books',_'value':_'books'}</t>
+          <t>picture_and_story_books</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Picture and Story Books', 'value': 'books'}</t>
+          <t>Picture and Story Books</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'paints_and_art_supplies',_'value':_'art'}</t>
+          <t>paints_and_art_supplies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Paints and Art Supplies', 'value': 'art'}</t>
+          <t>Paints and Art Supplies</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'outdoor_play_equipment',_'value':_'outdoor'}</t>
+          <t>outdoor_play_equipment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Outdoor Play Equipment', 'value': 'outdoor'}</t>
+          <t>Outdoor Play Equipment</t>
         </is>
       </c>
     </row>
